--- a/Test data/testdataregister.xlsx
+++ b/Test data/testdataregister.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">fullname</t>
   </si>
@@ -43,6 +43,15 @@
     <t xml:space="preserve">billpayamount</t>
   </si>
   <si>
+    <t xml:space="preserve">cardnumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cardholdername</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cvv</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nandalal7</t>
   </si>
   <si>
@@ -53,14 +62,18 @@
   </si>
   <si>
     <t xml:space="preserve">ZKxczsQBhPctcJEjDcfLWQ==</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nandalal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -127,8 +140,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -149,12 +170,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -179,28 +203,46 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10000</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>5000</v>
+        <v>3000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1234567888999890</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Test data/testdataregister.xlsx
+++ b/Test data/testdataregister.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Nandaal7@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">ZKxczsQBhPctcJEjDcfLWQ==</t>
+    <t xml:space="preserve">nx8lW3ljSW9sOmyu/baZlw==</t>
   </si>
   <si>
     <t xml:space="preserve">Nandalal</t>
